--- a/etf_holdings/2026-10-29_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-10-29_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2415</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5010</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.49%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4045</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.45%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1040</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.42%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3105</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.47%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6405</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.73%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>543</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.38%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>4840</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.52%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1480</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.85%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1250</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.31%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1755</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.09%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1390</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.77%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>115.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.91%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1115</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:31</t>
+          <t>2026-10-29 23:31:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.73%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>683</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:35</t>
+          <t>2026-10-29 23:32:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:36</t>
+          <t>2026-10-29 23:32:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:38</t>
+          <t>2026-10-29 23:32:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3599,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3660,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3721,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3782,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3904,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3965,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +4026,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4087,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4209,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4331,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4392,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4453,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:44</t>
+          <t>2026-10-29 23:32:33</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4514,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4636,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4697,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4758,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4819,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4880,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4941,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +5002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5063,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5124,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5246,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5307,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5368,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:46</t>
+          <t>2026-10-29 23:32:34</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5429,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5490,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5551,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5612,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5673,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5795,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5856,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5917,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5978,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6039,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6100,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6161,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6283,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:47</t>
+          <t>2026-10-29 23:32:36</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6344,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:48</t>
+          <t>2026-10-29 23:32:37</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6405,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:48</t>
+          <t>2026-10-29 23:32:37</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6466,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:48</t>
+          <t>2026-10-29 23:32:37</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6527,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:48</t>
+          <t>2026-10-29 23:32:37</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6588,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:48</t>
+          <t>2026-10-29 23:32:37</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6649,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6710,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6771,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6832,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6893,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6954,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +7015,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7076,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7137,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7198,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7259,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7320,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7381,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7442,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7503,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:53</t>
+          <t>2026-10-29 23:32:42</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7564,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7625,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7686,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7747,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7808,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7869,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7930,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7991,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8052,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8113,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8174,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8235,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8296,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8357,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8418,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:54</t>
+          <t>2026-10-29 23:32:43</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8479,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8540,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8601,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8662,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8723,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8784,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8845,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8906,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8967,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +9028,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9089,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9150,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9211,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9272,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9333,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:55</t>
+          <t>2026-10-29 23:32:44</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9394,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9455,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9516,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9577,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9638,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-10-29 23:19:57</t>
+          <t>2026-10-29 23:32:46</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9699,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9760,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9821,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9882,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9943,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +10004,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10065,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10126,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10187,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10309,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10370,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10492,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10553,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:01</t>
+          <t>2026-10-29 23:32:51</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10614,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10675,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10736,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10797,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10858,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10919,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10980,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11041,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11102,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11163,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11224,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11285,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11346,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11407,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:02</t>
+          <t>2026-10-29 23:32:53</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11529,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11590,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11651,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11712,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11773,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11834,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11895,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11956,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +12017,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12078,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12139,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12200,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12261,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12322,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12383,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:04</t>
+          <t>2026-10-29 23:32:54</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12444,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12505,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12566,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12627,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12688,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12749,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12810,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12871,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12932,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12993,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13054,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13115,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13176,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:05</t>
+          <t>2026-10-29 23:32:55</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13237,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13298,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13359,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13420,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13481,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13542,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13603,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13664,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13725,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13847,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13908,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13969,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14030,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14091,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:09</t>
+          <t>2026-10-29 23:33:01</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14152,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14213,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14274,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14335,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14396,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14457,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14518,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14579,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14640,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14701,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14762,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14823,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14884,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14945,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +15006,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:10</t>
+          <t>2026-10-29 23:33:02</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15067,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15128,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15189,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15250,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15311,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15372,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15433,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15494,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15555,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15616,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15677,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15738,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15799,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15860,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15921,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:12</t>
+          <t>2026-10-29 23:33:04</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15982,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16043,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16104,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16226,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-10-29 23:20:13</t>
+          <t>2026-10-29 23:33:05</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16287,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16348,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16409,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16470,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16531,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16592,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16653,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16714,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16775,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16836,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16897,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16958,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +17019,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17080,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17141,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:18</t>
+          <t>2026-10-29 23:34:15</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17202,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17263,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17324,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17385,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17446,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17507,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17568,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17629,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17690,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17751,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17812,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17873,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17934,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17995,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18056,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:20</t>
+          <t>2026-10-29 23:34:16</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18117,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18178,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18239,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18300,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18422,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18483,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18544,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18605,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18666,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18727,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18788,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18849,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:21</t>
+          <t>2026-10-29 23:34:17</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18910,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:26</t>
+          <t>2026-10-29 23:34:24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18943,7 +18973,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19006,7 +19036,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19069,7 +19099,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19132,7 +19162,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19195,7 +19225,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19258,7 +19288,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:27</t>
+          <t>2026-10-29 23:34:25</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19321,7 +19351,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19384,7 +19414,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19447,7 +19477,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19510,7 +19540,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:29</t>
+          <t>2026-10-29 23:34:27</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19573,7 +19603,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19634,7 +19664,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19695,7 +19725,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19756,7 +19786,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19817,7 +19847,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19878,7 +19908,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19939,7 +19969,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -20000,7 +20030,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20061,7 +20091,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20122,7 +20152,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20183,7 +20213,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20244,7 +20274,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20305,7 +20335,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20366,7 +20396,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20427,7 +20457,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:33</t>
+          <t>2026-10-29 23:34:33</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20488,7 +20518,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20549,7 +20579,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20610,7 +20640,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20671,7 +20701,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20732,7 +20762,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20793,7 +20823,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20854,7 +20884,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20915,7 +20945,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20976,7 +21006,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21037,7 +21067,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21098,7 +21128,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21159,7 +21189,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21220,7 +21250,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21281,7 +21311,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21342,7 +21372,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:35</t>
+          <t>2026-10-29 23:34:34</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21403,7 +21433,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21464,7 +21494,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21525,7 +21555,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21586,7 +21616,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21647,7 +21677,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21708,7 +21738,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21769,7 +21799,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21830,7 +21860,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21891,7 +21921,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21952,7 +21982,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -22013,7 +22043,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22074,7 +22104,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22135,7 +22165,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22196,7 +22226,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22257,7 +22287,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:36</t>
+          <t>2026-10-29 23:34:36</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22318,7 +22348,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22379,7 +22409,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22440,7 +22470,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22501,7 +22531,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22562,7 +22592,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22623,7 +22653,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22684,7 +22714,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22745,7 +22775,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22806,7 +22836,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22867,7 +22897,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22928,7 +22958,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -22989,7 +23019,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23050,7 +23080,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23111,7 +23141,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23172,7 +23202,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23233,7 +23263,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23294,7 +23324,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23355,7 +23385,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23416,7 +23446,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23477,7 +23507,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23538,7 +23568,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23599,7 +23629,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23660,7 +23690,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23721,7 +23751,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23782,7 +23812,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23843,7 +23873,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23904,7 +23934,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23965,7 +23995,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24026,7 +24056,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24087,7 +24117,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24148,7 +24178,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24209,7 +24239,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24270,7 +24300,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24331,7 +24361,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24392,7 +24422,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24453,7 +24483,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24514,7 +24544,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24575,7 +24605,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24636,7 +24666,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24697,7 +24727,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24758,7 +24788,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24819,7 +24849,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24880,7 +24910,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24941,7 +24971,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25002,7 +25032,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25063,7 +25093,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25124,7 +25154,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25185,7 +25215,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25246,7 +25276,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25307,7 +25337,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25368,7 +25398,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25429,7 +25459,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25490,7 +25520,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25551,7 +25581,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25612,7 +25642,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25673,7 +25703,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25734,7 +25764,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25795,7 +25825,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25856,7 +25886,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25917,7 +25947,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25978,7 +26008,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26039,7 +26069,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26100,7 +26130,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26161,7 +26191,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26222,7 +26252,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:52</t>
+          <t>2026-10-29 23:34:52</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26283,7 +26313,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26344,7 +26374,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26405,7 +26435,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26466,7 +26496,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26527,7 +26557,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26588,7 +26618,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26649,7 +26679,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26710,7 +26740,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26771,7 +26801,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26832,7 +26862,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26893,7 +26923,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26954,7 +26984,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27015,7 +27045,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27076,7 +27106,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27137,7 +27167,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:53</t>
+          <t>2026-10-29 23:34:53</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27198,7 +27228,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27259,7 +27289,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27320,7 +27350,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27381,7 +27411,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27442,7 +27472,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27503,7 +27533,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27564,7 +27594,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27625,7 +27655,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27686,7 +27716,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27747,7 +27777,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27808,7 +27838,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27869,7 +27899,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27930,7 +27960,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -27991,7 +28021,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28052,7 +28082,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:55</t>
+          <t>2026-10-29 23:34:55</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28113,7 +28143,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:56</t>
+          <t>2026-10-29 23:34:56</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28174,7 +28204,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:56</t>
+          <t>2026-10-29 23:34:56</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28235,7 +28265,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:56</t>
+          <t>2026-10-29 23:34:56</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28296,7 +28326,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:56</t>
+          <t>2026-10-29 23:34:56</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28357,7 +28387,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:56</t>
+          <t>2026-10-29 23:34:56</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28418,7 +28448,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28479,7 +28509,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28540,7 +28570,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28601,7 +28631,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28662,7 +28692,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28723,7 +28753,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28784,7 +28814,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28845,7 +28875,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28906,7 +28936,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28967,7 +28997,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29028,7 +29058,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29089,7 +29119,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29150,7 +29180,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29211,7 +29241,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29272,7 +29302,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:01</t>
+          <t>2026-10-29 23:35:03</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29333,7 +29363,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29394,7 +29424,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29455,7 +29485,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29516,7 +29546,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29577,7 +29607,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29638,7 +29668,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29699,7 +29729,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29760,7 +29790,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29821,7 +29851,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29882,7 +29912,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29943,7 +29973,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30004,7 +30034,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30065,7 +30095,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30126,7 +30156,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30187,7 +30217,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:02</t>
+          <t>2026-10-29 23:35:05</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30248,7 +30278,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30309,7 +30339,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30370,7 +30400,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30431,7 +30461,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30492,7 +30522,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30553,7 +30583,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30614,7 +30644,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30675,7 +30705,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30736,7 +30766,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30797,7 +30827,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30858,7 +30888,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30919,7 +30949,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30980,7 +31010,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31041,7 +31071,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31102,7 +31132,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:03</t>
+          <t>2026-10-29 23:35:06</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31163,7 +31193,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31224,7 +31254,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31285,7 +31315,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31346,7 +31376,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31407,7 +31437,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31468,7 +31498,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31529,7 +31559,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31590,7 +31620,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-10-29 23:22:05</t>
+          <t>2026-10-29 23:35:07</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
